--- a/data/trans_dic/IP21-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,77</t>
+          <t>2,79; 13,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,57</t>
+          <t>0,82; 8,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,67</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 12,16</t>
+          <t>2,13; 12,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,34</t>
+          <t>2,47; 14,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 15,77</t>
+          <t>2,92; 15,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 7,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,89</t>
+          <t>3,19; 10,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,27</t>
+          <t>1,41; 7,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,67</t>
+          <t>2,49; 9,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,82</t>
+          <t>0,57; 5,31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,13</t>
+          <t>2,34; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,21</t>
+          <t>1,85; 8,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,42</t>
+          <t>1,12; 6,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,11</t>
+          <t>0,41; 5,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,03</t>
+          <t>2,4; 9,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,9</t>
+          <t>2,85; 9,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,51</t>
+          <t>0,69; 6,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,12</t>
+          <t>0,4; 4,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,61</t>
+          <t>2,99; 7,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,81</t>
+          <t>2,99; 7,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,02</t>
+          <t>1,41; 5,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,59</t>
+          <t>0,66; 4,07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,66</t>
+          <t>2,21; 12,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,29</t>
+          <t>0,92; 9,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,08</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,86</t>
+          <t>1,0; 9,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 12,4</t>
+          <t>2,69; 12,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 12,06</t>
+          <t>2,05; 11,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,14</t>
+          <t>0,95; 7,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,49</t>
+          <t>3,29; 9,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,16</t>
+          <t>2,42; 8,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,49</t>
+          <t>0,97; 5,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,38</t>
+          <t>0,87; 5,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,2</t>
+          <t>0,71; 7,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,81</t>
+          <t>0,56; 6,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,2</t>
+          <t>0,97; 8,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,13</t>
+          <t>1,89; 10,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 11,5</t>
+          <t>1,62; 12,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,13</t>
+          <t>0,85; 7,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,62</t>
+          <t>2,15; 7,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,26</t>
+          <t>1,58; 7,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,06</t>
+          <t>1,32; 6,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,5</t>
+          <t>1,67; 14,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 13,21</t>
+          <t>1,59; 11,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,05</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,27</t>
+          <t>1,46; 14,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,27</t>
+          <t>1,48; 8,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,97</t>
+          <t>2,28; 10,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,16</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 15,24</t>
+          <t>2,71; 15,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 10,74</t>
+          <t>0,76; 10,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 11,46</t>
+          <t>1,05; 10,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 8,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 8,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,72</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,16</t>
+          <t>1,23; 7,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,71</t>
+          <t>2,17; 9,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,33</t>
+          <t>0,69; 6,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,93</t>
+          <t>0,69; 6,03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,19</t>
+          <t>0,52; 5,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,38; 10,84</t>
+          <t>3,61; 10,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,18</t>
+          <t>2,8; 9,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,61</t>
+          <t>0,33; 4,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,17</t>
+          <t>2,65; 9,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,66</t>
+          <t>1,72; 6,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,42</t>
+          <t>0,82; 4,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,88</t>
+          <t>1,12; 6,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,17</t>
+          <t>2,36; 6,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,45</t>
+          <t>3,25; 7,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,95</t>
+          <t>2,21; 5,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,79</t>
+          <t>1,01; 4,54</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,44</t>
+          <t>0,66; 4,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,91</t>
+          <t>0,82; 5,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,03</t>
+          <t>1,09; 5,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,27</t>
+          <t>1,64; 6,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,79</t>
+          <t>1,5; 5,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,83</t>
+          <t>1,06; 4,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,57</t>
+          <t>1,43; 4,47</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,55</t>
+          <t>1,64; 4,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,96</t>
+          <t>1,22; 3,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,03</t>
+          <t>2,7; 4,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,43</t>
+          <t>2,94; 5,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,2</t>
+          <t>2,12; 4,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,27</t>
+          <t>0,75; 2,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,16</t>
+          <t>3,5; 5,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,91</t>
+          <t>3,34; 5,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,02</t>
+          <t>1,9; 3,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,66</t>
+          <t>0,98; 2,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,1</t>
+          <t>3,35; 5,07</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,15</t>
+          <t>3,51; 5,08</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,64</t>
+          <t>2,27; 3,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,24</t>
+          <t>1,0; 2,16</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6498</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1469; 6882</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>469; 5006</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1280; 7474</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1599; 9329</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1880; 9780</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6048</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3596; 11731</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1724; 9627</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3033; 11909</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>877; 8104</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4523</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2985</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2085</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10183</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>10938</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4258</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2381; 9235</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1937; 9076</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1167; 6637</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>518; 6749</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2611; 9815</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3168; 11105</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>759; 7340</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>514; 5972</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6292; 16038</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6460; 16822</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3011; 11346</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1679; 10351</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4188</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1918</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4390</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4158</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8578</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6873</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3392</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1496; 8734</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>628; 6167</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4637</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>581; 5256</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1888; 8773</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1434; 7958</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>665; 5252</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3834</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4543; 13773</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3341; 12108</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7577</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1088; 6454</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6499</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6069</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4868</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>535; 5867</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>437; 4816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747; 6461</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2479</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1496; 8332</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1328; 9895</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>693; 6455</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2619</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3306; 11699</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2532; 12162</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2090; 9494</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3590</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>700; 6127</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698; 5076</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3370</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>673; 6490</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1284; 6966</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2051; 9063</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4293</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2985</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4164</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1516; 8796</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4279</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>353; 4620</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>626; 6409</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4935</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4688</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3859</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1430; 8197</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2527; 10705</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>771; 7456</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>711; 6169</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8815</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1674</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5137</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>10483</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13952</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>6487</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>668; 6652</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5011; 15005</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3849; 12550</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>415; 5049</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3592; 12775</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2483; 9550</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1175; 6294</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1750; 10832</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6228; 16944</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>9203; 20902</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6212; 16402</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2841; 12747</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3996</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3867</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>8726</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>9314</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7879</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1044; 7309</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1355; 8316</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1775; 8374</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2693; 10239</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2568; 10113</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1812; 8425</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4544</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4597; 14386</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>5488; 15113</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>4081; 13114</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4600</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>25411</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>28704</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>21228</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>9215</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>12461</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>58565</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>61926</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>41925</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>21675</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>18367; 34016</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>20920; 38098</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14921; 29168</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>5003; 15333</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>25312; 42986</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>25045; 42564</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>14159; 29730</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>7477; 19516</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>47014; 71123</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>51365; 74303</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>32805; 53651</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>14264; 30799</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 13,09</t>
+          <t>2,25; 13,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,73</t>
+          <t>0,81; 8,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,41</t>
+          <t>2,17; 12,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,39</t>
+          <t>2,45; 13,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 15,17</t>
+          <t>2,53; 14,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,62</t>
+          <t>0,0; 7,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,4</t>
+          <t>3,26; 10,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,88</t>
+          <t>1,42; 7,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,78</t>
+          <t>2,74; 10,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,31</t>
+          <t>0,52; 4,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,09</t>
+          <t>2,35; 9,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,67</t>
+          <t>1,84; 8,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,38</t>
+          <t>1,1; 6,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,34</t>
+          <t>0,34; 5,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,03</t>
+          <t>2,36; 8,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,99</t>
+          <t>2,88; 10,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,66</t>
+          <t>0,68; 6,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,68</t>
+          <t>0,4; 5,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,63</t>
+          <t>2,74; 7,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,79</t>
+          <t>3,01; 7,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,3</t>
+          <t>1,19; 4,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,07</t>
+          <t>0,61; 3,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 12,92</t>
+          <t>2,96; 12,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,05</t>
+          <t>1,06; 9,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,02</t>
+          <t>1,0; 10,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 12,48</t>
+          <t>2,66; 12,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,39</t>
+          <t>2,13; 12,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,51</t>
+          <t>0,95; 8,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,0; 6,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,99</t>
+          <t>3,39; 10,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,77</t>
+          <t>2,49; 8,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,54</t>
+          <t>0,97; 5,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,15</t>
+          <t>0,9; 5,24</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,84</t>
+          <t>0,82; 7,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,19</t>
+          <t>0,57; 6,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,4</t>
+          <t>0,96; 8,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 10,53</t>
+          <t>2,37; 10,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 12,03</t>
+          <t>1,76; 11,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,95</t>
+          <t>0,85; 7,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,6</t>
+          <t>2,3; 7,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,6</t>
+          <t>1,63; 7,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,0</t>
+          <t>1,35; 6,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,64</t>
+          <t>1,67; 15,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 11,56</t>
+          <t>0,0; 13,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,08</t>
+          <t>1,46; 14,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,03</t>
+          <t>1,5; 8,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 10,07</t>
+          <t>2,3; 10,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 15,71</t>
+          <t>3,69; 15,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 10,01</t>
+          <t>0,77; 10,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,73</t>
+          <t>1,05; 11,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 10,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,08</t>
+          <t>1,15; 7,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,21</t>
+          <t>1,89; 9,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,66</t>
+          <t>0,69; 6,61</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,03</t>
+          <t>0,94; 5,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,17</t>
+          <t>1,0; 5,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,82</t>
+          <t>3,4; 10,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,14</t>
+          <t>2,63; 8,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,06</t>
+          <t>0,34; 3,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 9,42</t>
+          <t>2,72; 9,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,6</t>
+          <t>1,76; 6,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,37</t>
+          <t>0,86; 5,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,94</t>
+          <t>1,25; 6,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,41</t>
+          <t>2,23; 6,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,37</t>
+          <t>2,94; 7,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,83</t>
+          <t>2,2; 5,46</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,54</t>
+          <t>1,18; 4,54</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,63</t>
+          <t>0,67; 4,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,05</t>
+          <t>0,85; 5,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,14</t>
+          <t>1,07; 5,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,24</t>
+          <t>1,3; 6,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,92</t>
+          <t>1,44; 5,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,93</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,47</t>
+          <t>1,5; 4,53</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,51</t>
+          <t>1,7; 4,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,93</t>
+          <t>1,19; 3,94</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,99</t>
+          <t>2,66; 4,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,36</t>
+          <t>2,86; 5,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,15</t>
+          <t>2,15; 4,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,31</t>
+          <t>0,82; 2,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,95</t>
+          <t>3,36; 5,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,68</t>
+          <t>3,37; 5,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,99</t>
+          <t>1,83; 3,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,56</t>
+          <t>0,97; 2,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,07</t>
+          <t>3,39; 5,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,08</t>
+          <t>3,42; 5,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,71</t>
+          <t>2,25; 3,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,16</t>
+          <t>1,02; 2,09</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1469; 6882</t>
+          <t>1182; 6841</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2393</t>
+          <t>0; 2674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>469; 5006</t>
+          <t>467; 4802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 4007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1280; 7474</t>
+          <t>1307; 7437</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1599; 9329</t>
+          <t>1585; 8658</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1880; 9780</t>
+          <t>1631; 9313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6048</t>
+          <t>0; 6054</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3596; 11731</t>
+          <t>3678; 11517</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1724; 9627</t>
+          <t>1732; 9675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3033; 11909</t>
+          <t>3343; 12331</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>877; 8104</t>
+          <t>788; 6765</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2381; 9235</t>
+          <t>2383; 9305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1937; 9076</t>
+          <t>1926; 9072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1167; 6637</t>
+          <t>1145; 6383</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518; 6749</t>
+          <t>433; 7185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2611; 9815</t>
+          <t>2569; 9296</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3168; 11105</t>
+          <t>3203; 11501</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>759; 7340</t>
+          <t>747; 7291</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>514; 5972</t>
+          <t>508; 6530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6292; 16038</t>
+          <t>5763; 15884</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6460; 16822</t>
+          <t>6487; 16671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3011; 11346</t>
+          <t>2551; 10587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1679; 10351</t>
+          <t>1554; 9304</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1496; 8734</t>
+          <t>2001; 8448</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>628; 6167</t>
+          <t>723; 6779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4637</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>581; 5256</t>
+          <t>582; 5925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1888; 8773</t>
+          <t>1872; 8730</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1434; 7958</t>
+          <t>1487; 8856</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>665; 5252</t>
+          <t>667; 5604</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 4248</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4543; 13773</t>
+          <t>4670; 14389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3341; 12108</t>
+          <t>3439; 11865</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1320; 7577</t>
+          <t>1325; 7476</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1088; 6454</t>
+          <t>1124; 6572</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>535; 5867</t>
+          <t>614; 5844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>437; 4816</t>
+          <t>445; 5192</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>747; 6461</t>
+          <t>742; 6404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2479</t>
+          <t>0; 2833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1496; 8332</t>
+          <t>1874; 8598</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1328; 9895</t>
+          <t>1450; 9675</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>693; 6455</t>
+          <t>694; 6030</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3306; 11699</t>
+          <t>3547; 11869</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2532; 12162</t>
+          <t>2606; 12224</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2090; 9494</t>
+          <t>2139; 9884</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3590</t>
+          <t>0; 3513</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>700; 6127</t>
+          <t>700; 6568</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>698; 5076</t>
+          <t>0; 5756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3370</t>
+          <t>0; 4167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>673; 6490</t>
+          <t>672; 6770</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1284; 6966</t>
+          <t>1298; 7332</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2051; 9063</t>
+          <t>2071; 9731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4164</t>
+          <t>0; 4038</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1516; 8796</t>
+          <t>2066; 8653</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4279</t>
+          <t>0; 4925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>353; 4620</t>
+          <t>356; 4905</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>626; 6409</t>
+          <t>628; 6667</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4935</t>
+          <t>0; 6410</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4688</t>
+          <t>0; 5499</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3859</t>
+          <t>0; 3840</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1430; 8197</t>
+          <t>1329; 8164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2527; 10705</t>
+          <t>2192; 10882</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>771; 7456</t>
+          <t>768; 7408</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>711; 6169</t>
+          <t>967; 5837</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>668; 6652</t>
+          <t>1286; 6672</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5011; 15005</t>
+          <t>4719; 14707</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3849; 12550</t>
+          <t>3616; 12247</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>415; 5049</t>
+          <t>421; 4839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3592; 12775</t>
+          <t>3692; 12578</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2483; 9550</t>
+          <t>2546; 9806</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1175; 6294</t>
+          <t>1242; 7448</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1750; 10832</t>
+          <t>1947; 10760</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6228; 16944</t>
+          <t>5888; 16329</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9203; 20902</t>
+          <t>8335; 20482</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6212; 16402</t>
+          <t>6187; 15373</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2841; 12747</t>
+          <t>3320; 12747</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1044; 7309</t>
+          <t>1057; 6869</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1355; 8316</t>
+          <t>1403; 8318</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1775; 8374</t>
+          <t>1748; 8221</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,42 +3685,42 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2693; 10239</t>
+          <t>2125; 10194</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2568; 10113</t>
+          <t>2459; 10096</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1812; 8425</t>
+          <t>1528; 8807</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>0; 4291</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4597; 14386</t>
+          <t>4832; 14598</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5488; 15113</t>
+          <t>5712; 15676</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4081; 13114</t>
+          <t>3969; 13145</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4600</t>
+          <t>0; 4797</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18367; 34016</t>
+          <t>18081; 33917</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20920; 38098</t>
+          <t>20332; 37653</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14921; 29168</t>
+          <t>15132; 29261</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5003; 15333</t>
+          <t>5478; 15592</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>25312; 42986</t>
+          <t>24286; 43268</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25045; 42564</t>
+          <t>25249; 43870</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14159; 29730</t>
+          <t>13633; 29319</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7477; 19516</t>
+          <t>7426; 20256</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>47014; 71123</t>
+          <t>47626; 72464</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51365; 74303</t>
+          <t>49961; 76239</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32805; 53651</t>
+          <t>32566; 54318</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14264; 30799</t>
+          <t>14607; 29838</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP21-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,57%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,01</t>
+          <t>2,21; 12,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>2,16; 14,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,37</t>
+          <t>3,12; 15,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,35</t>
+          <t>2,24; 13,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,36</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,45</t>
+          <t>0,8; 7,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,63</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,21</t>
+          <t>3,37; 9,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,91</t>
+          <t>1,64; 8,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 10,12</t>
+          <t>2,79; 9,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,43</t>
+          <t>0,56; 5,19</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,86%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 9,16</t>
+          <t>2,38; 9,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,66</t>
+          <t>2,87; 9,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,14</t>
+          <t>0,68; 6,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,68</t>
+          <t>0,35; 4,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,55</t>
+          <t>1,85; 9,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,35</t>
+          <t>1,83; 8,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,61</t>
+          <t>1,1; 6,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,12</t>
+          <t>0,52; 6,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,55</t>
+          <t>3,0; 7,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,72</t>
+          <t>2,97; 7,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,94</t>
+          <t>1,25; 5,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,66</t>
+          <t>0,66; 3,94</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,2%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 12,5</t>
+          <t>2,68; 12,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,94</t>
+          <t>2,04; 12,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,95; 9,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,17</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 12,41</t>
+          <t>2,1; 12,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,67</t>
+          <t>0,93; 9,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,02</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,33</t>
+          <t>1,02; 9,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,43</t>
+          <t>3,67; 10,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,59</t>
+          <t>2,52; 9,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,47</t>
+          <t>0,97; 5,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,24</t>
+          <t>0,91; 5,53</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,54%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>0,68%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,81</t>
+          <t>2,36; 11,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,68</t>
+          <t>1,69; 11,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,32</t>
+          <t>0,0; 7,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,87</t>
+          <t>0,84; 7,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,76</t>
+          <t>0,56; 6,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,43</t>
+          <t>0,99; 9,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,71</t>
+          <t>2,12; 7,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,64</t>
+          <t>1,69; 7,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,25</t>
+          <t>1,31; 6,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
     </row>
@@ -1209,32 +1209,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,38%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,85%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,69</t>
+          <t>0,0; 9,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,11</t>
+          <t>1,46; 13,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>1,51; 14,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,68</t>
+          <t>1,58; 13,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,46</t>
+          <t>1,49; 8,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 10,81</t>
+          <t>2,25; 9,97</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7,67%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,63%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>1,03; 11,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 15,46</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 10,62</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 11,16</t>
+          <t>0,0; 8,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,64</t>
+          <t>2,63; 15,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,83</t>
+          <t>0,56; 9,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 7,05</t>
+          <t>1,57; 7,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,36</t>
+          <t>1,87; 8,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,61</t>
+          <t>0,69; 6,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,7</t>
+          <t>0,84; 5,49</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,35%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,19</t>
+          <t>2,72; 9,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,6</t>
+          <t>1,73; 6,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,91</t>
+          <t>0,86; 4,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,89</t>
+          <t>1,25; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,27</t>
+          <t>0,98; 5,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,77</t>
+          <t>3,38; 10,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,17</t>
+          <t>2,84; 9,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,9</t>
+          <t>0,3; 3,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,18</t>
+          <t>2,33; 6,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,23</t>
+          <t>3,07; 7,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,46</t>
+          <t>2,27; 5,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,54</t>
+          <t>1,12; 5,04</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2,71%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,35</t>
+          <t>1,67; 6,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,05</t>
+          <t>1,5; 5,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,05</t>
+          <t>0,84; 4,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,37</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,76; 4,44</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,84; 4,91</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,82; 5,03</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 6,21</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 5,91</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,89; 5,15</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,74</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,53</t>
+          <t>1,58; 4,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,67</t>
+          <t>1,58; 4,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,94</t>
+          <t>1,21; 3,96</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,98</t>
+          <t>3,42; 6,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,29</t>
+          <t>3,31; 5,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,16</t>
+          <t>1,93; 4,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,34</t>
+          <t>0,95; 2,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,99</t>
+          <t>2,72; 5,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,85</t>
+          <t>2,9; 5,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,94</t>
+          <t>2,16; 4,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,66</t>
+          <t>0,77; 2,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,16</t>
+          <t>3,38; 5,1</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,22</t>
+          <t>3,41; 5,15</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,75</t>
+          <t>2,22; 3,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,09</t>
+          <t>1,05; 2,24</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses (tasa de respuesta: 99,9%)</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3452</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1698</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4800</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2562</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1182; 6841</t>
+          <t>1330; 7320</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2674</t>
+          <t>1398; 9293</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>467; 4802</t>
+          <t>2011; 10164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4007</t>
+          <t>0; 5143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1307; 7437</t>
+          <t>1178; 7238</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1585; 8658</t>
+          <t>0; 2841</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1631; 9313</t>
+          <t>459; 4342</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6054</t>
+          <t>0; 3724</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3678; 11517</t>
+          <t>3797; 11155</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1732; 9675</t>
+          <t>2002; 10111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3343; 12331</t>
+          <t>3398; 11784</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>788; 6765</t>
+          <t>675; 6257</t>
         </is>
       </c>
     </row>
@@ -2286,32 +2286,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2985</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4937</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4523</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3006</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2173</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6416</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2985</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4037</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2383; 9305</t>
+          <t>2584; 9819</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1926; 9072</t>
+          <t>3194; 11008</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1145; 6383</t>
+          <t>755; 7179</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>433; 7185</t>
+          <t>406; 5742</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2569; 9296</t>
+          <t>1879; 9271</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3203; 11501</t>
+          <t>1920; 8598</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>747; 7291</t>
+          <t>1148; 6674</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>508; 6530</t>
+          <t>522; 6363</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5763; 15884</t>
+          <t>6307; 16009</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6487; 16671</t>
+          <t>6402; 16855</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2551; 10587</t>
+          <t>2687; 10764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1554; 9304</t>
+          <t>1417; 8501</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4390</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4158</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4188</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2715</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1318</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4390</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4158</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2831</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2001; 8448</t>
+          <t>1885; 8720</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>723; 6779</t>
+          <t>1428; 8429</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4135</t>
+          <t>667; 6387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>582; 5925</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1872; 8730</t>
+          <t>1417; 8556</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1487; 8856</t>
+          <t>634; 6336</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>667; 5604</t>
+          <t>0; 4061</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4248</t>
+          <t>577; 5168</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4670; 14389</t>
+          <t>5060; 14465</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3439; 11865</t>
+          <t>3479; 12645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1325; 7476</t>
+          <t>1330; 7507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1124; 6572</t>
+          <t>1051; 6410</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2301</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1755</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2724</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4198</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4314</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>516</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>969</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>614; 5844</t>
+          <t>1865; 8807</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>445; 5192</t>
+          <t>1392; 9455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>742; 6404</t>
+          <t>0; 5791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2833</t>
+          <t>0; 2401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1874; 8598</t>
+          <t>626; 5387</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1450; 9675</t>
+          <t>437; 5299</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>694; 6030</t>
+          <t>764; 7079</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>0; 3026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3547; 11869</t>
+          <t>3272; 11732</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2606; 12224</t>
+          <t>2704; 11615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2139; 9884</t>
+          <t>2072; 9582</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3082</t>
         </is>
       </c>
     </row>
@@ -2905,32 +2905,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,32 +2973,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2669</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2129</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>700; 6568</t>
+          <t>0; 4056</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5756</t>
+          <t>675; 6117</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4167</t>
+          <t>633; 6070</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>672; 6770</t>
+          <t>695; 5797</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1298; 7332</t>
+          <t>1295; 7166</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2071; 9731</t>
+          <t>2028; 8977</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1330</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4293</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1428</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2214</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4038</t>
+          <t>618; 6843</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2066; 8653</t>
+          <t>0; 4471</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4925</t>
+          <t>0; 4796</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>356; 4905</t>
+          <t>0; 2956</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>628; 6667</t>
+          <t>0; 4575</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6410</t>
+          <t>1472; 8534</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5499</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3840</t>
+          <t>257; 4442</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1329; 8164</t>
+          <t>1819; 8291</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2192; 10882</t>
+          <t>2179; 10126</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>768; 7408</t>
+          <t>772; 7095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>967; 5837</t>
+          <t>799; 5201</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5137</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3124</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4754</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>3288</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>8815</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>7187</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1674</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7195</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5137</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6350</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1286; 6672</t>
+          <t>3686; 12436</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4719; 14707</t>
+          <t>2508; 9635</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3616; 12247</t>
+          <t>1237; 6369</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>421; 4839</t>
+          <t>1768; 11170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3692; 12578</t>
+          <t>1254; 6678</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2546; 9806</t>
+          <t>4694; 15032</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1242; 7448</t>
+          <t>3906; 12613</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1947; 10760</t>
+          <t>364; 4606</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5888; 16329</t>
+          <t>6164; 16317</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8335; 20482</t>
+          <t>8714; 21121</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6187; 15373</t>
+          <t>6398; 16756</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3320; 12747</t>
+          <t>2961; 13298</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1197</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3246</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3996</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>3867</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>8726</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1197</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1057; 6869</t>
+          <t>2736; 10280</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1403; 8318</t>
+          <t>2558; 9878</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1748; 8221</t>
+          <t>1434; 8254</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>0; 5366</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1200; 7008</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1388; 8094</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1335; 8193</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2125; 10194</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>2459; 10096</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1528; 8807</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0; 4291</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4832; 14598</t>
+          <t>5102; 14723</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5712; 15676</t>
+          <t>5294; 15261</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3969; 13145</t>
+          <t>4041; 13235</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4797</t>
+          <t>0; 4891</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>18081; 33917</t>
+          <t>24714; 44527</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20332; 37653</t>
+          <t>24790; 44312</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15132; 29261</t>
+          <t>14379; 29947</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5478; 15592</t>
+          <t>6636; 18992</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24286; 43268</t>
+          <t>18554; 34256</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25249; 43870</t>
+          <t>20624; 38603</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13633; 29319</t>
+          <t>15183; 29522</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7426; 20256</t>
+          <t>4829; 14576</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>47626; 72464</t>
+          <t>47391; 71554</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49961; 76239</t>
+          <t>49795; 75301</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32566; 54318</t>
+          <t>32181; 52655</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14607; 29838</t>
+          <t>13960; 29765</t>
         </is>
       </c>
     </row>
